--- a/data/processed/harmonization/Carbon__Soil_organic_matter/harmonized.xlsx
+++ b/data/processed/harmonization/Carbon__Soil_organic_matter/harmonized.xlsx
@@ -432,7 +432,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="29" customWidth="1" min="7" max="7"/>
@@ -19802,12 +19802,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0209</t>
+          <t>upland:10.58052/IEEXG0209</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr"/>
@@ -19850,12 +19850,12 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020N</t>
+          <t>transition:10.58052/IEEXG020N</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr"/>
@@ -19898,12 +19898,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0211</t>
+          <t>wetland:10.58052/IEEXG0211</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr"/>
@@ -19946,12 +19946,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021F</t>
+          <t>upland:10.58052/IEEXG021F</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr"/>
@@ -19994,12 +19994,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021T</t>
+          <t>transition:10.58052/IEEXG021T</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr"/>
@@ -20042,12 +20042,12 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0227</t>
+          <t>wetland:10.58052/IEEXG0227</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr"/>
@@ -20090,12 +20090,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022L</t>
+          <t>upland:10.58052/IEEXG022L</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr"/>
@@ -20138,12 +20138,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022Z</t>
+          <t>transition:10.58052/IEEXG022Z</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr"/>
@@ -20186,12 +20186,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023D</t>
+          <t>wetland:10.58052/IEEXG023D</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr"/>
@@ -20234,12 +20234,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023R</t>
+          <t>upland:10.58052/IEEXG023R</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr"/>
@@ -20282,12 +20282,12 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0245</t>
+          <t>transition:10.58052/IEEXG0245</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr"/>
@@ -20330,12 +20330,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024J</t>
+          <t>wetland:10.58052/IEEXG024J</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr"/>
@@ -20378,12 +20378,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024X</t>
+          <t>upland:10.58052/IEEXG024X</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr"/>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025B</t>
+          <t>transition:10.58052/IEEXG025B</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr"/>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025P</t>
+          <t>wetland:10.58052/IEEXG025P</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr"/>
@@ -20522,12 +20522,12 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0263</t>
+          <t>upland:10.58052/IEEXG0263</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr"/>
@@ -20570,12 +20570,12 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026H</t>
+          <t>transition:10.58052/IEEXG026H</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr"/>
@@ -20618,12 +20618,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026V</t>
+          <t>wetland:10.58052/IEEXG026V</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr"/>
@@ -20666,12 +20666,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0279</t>
+          <t>upland:10.58052/IEEXG0279</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr"/>
@@ -20714,12 +20714,12 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027N</t>
+          <t>transition:10.58052/IEEXG027N</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr"/>
@@ -20762,12 +20762,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0281</t>
+          <t>wetland:10.58052/IEEXG0281</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr"/>
@@ -20810,12 +20810,12 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028F</t>
+          <t>upland:10.58052/IEEXG028F</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr"/>
@@ -20858,12 +20858,12 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028T</t>
+          <t>transition:10.58052/IEEXG028T</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr"/>
@@ -20906,12 +20906,12 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0297</t>
+          <t>wetland:10.58052/IEEXG0297</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr"/>
@@ -20954,12 +20954,12 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG029L</t>
+          <t>upland:10.58052/IEEXG029L</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr"/>
@@ -21002,12 +21002,12 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG029Z</t>
+          <t>transition:10.58052/IEEXG029Z</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr"/>
@@ -21050,12 +21050,12 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AD</t>
+          <t>wetland:10.58052/IEEXG02AD</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr"/>
@@ -21098,12 +21098,12 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AR</t>
+          <t>upland:10.58052/IEEXG02AR</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr"/>
@@ -21146,12 +21146,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02B5</t>
+          <t>transition:10.58052/IEEXG02B5</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr"/>
@@ -21194,12 +21194,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BJ</t>
+          <t>wetland:10.58052/IEEXG02BJ</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr"/>
@@ -21242,12 +21242,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BX</t>
+          <t>upland:10.58052/IEEXG02BX</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr"/>
@@ -21290,12 +21290,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CB</t>
+          <t>transition:10.58052/IEEXG02CB</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr"/>
@@ -21338,12 +21338,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CP</t>
+          <t>wetland:10.58052/IEEXG02CP</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr"/>
@@ -21386,12 +21386,12 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02D3</t>
+          <t>upland:10.58052/IEEXG02D3</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr"/>
@@ -21434,12 +21434,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DH</t>
+          <t>transition:10.58052/IEEXG02DH</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr"/>
@@ -21482,12 +21482,12 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DV</t>
+          <t>wetland:10.58052/IEEXG02DV</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr"/>
@@ -21530,12 +21530,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02E9</t>
+          <t>upland:10.58052/IEEXG02E9</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr"/>
@@ -21578,12 +21578,12 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EN</t>
+          <t>transition:10.58052/IEEXG02EN</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr"/>
@@ -21626,12 +21626,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02F1</t>
+          <t>wetland:10.58052/IEEXG02F1</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr"/>
@@ -21674,12 +21674,12 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FF</t>
+          <t>upland:10.58052/IEEXG02FF</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr"/>
@@ -21722,12 +21722,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FT</t>
+          <t>transition:10.58052/IEEXG02FT</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr"/>
@@ -21770,12 +21770,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02G7</t>
+          <t>wetland:10.58052/IEEXG02G7</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr"/>
@@ -21818,12 +21818,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GL</t>
+          <t>upland:10.58052/IEEXG02GL</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr"/>
@@ -21866,12 +21866,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GZ</t>
+          <t>transition:10.58052/IEEXG02GZ</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr"/>
@@ -21914,12 +21914,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HD</t>
+          <t>wetland:10.58052/IEEXG02HD</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr"/>
@@ -21962,12 +21962,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HR</t>
+          <t>upland:10.58052/IEEXG02HR</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr"/>
@@ -22010,12 +22010,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02I5</t>
+          <t>transition:10.58052/IEEXG02I5</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr"/>
@@ -22058,12 +22058,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IJ</t>
+          <t>wetland:10.58052/IEEXG02IJ</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr"/>
@@ -22106,12 +22106,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IX</t>
+          <t>upland:10.58052/IEEXG02IX</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr"/>
@@ -22154,12 +22154,12 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JB</t>
+          <t>transition:10.58052/IEEXG02JB</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr"/>
@@ -22202,12 +22202,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JP</t>
+          <t>wetland:10.58052/IEEXG02JP</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr"/>
@@ -22250,12 +22250,12 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02K3</t>
+          <t>upland:10.58052/IEEXG02K3</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr"/>
@@ -22298,12 +22298,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KH</t>
+          <t>transition:10.58052/IEEXG02KH</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr"/>
@@ -22346,12 +22346,12 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KV</t>
+          <t>wetland:10.58052/IEEXG02KV</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr"/>
@@ -22394,12 +22394,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02L9</t>
+          <t>upland:10.58052/IEEXG02L9</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr"/>
@@ -22442,12 +22442,12 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LN</t>
+          <t>transition:10.58052/IEEXG02LN</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr"/>
@@ -22490,12 +22490,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02M1</t>
+          <t>wetland:10.58052/IEEXG02M1</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr"/>
@@ -22538,12 +22538,12 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MF</t>
+          <t>upland:10.58052/IEEXG02MF</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr"/>
@@ -22586,12 +22586,12 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MT</t>
+          <t>transition:10.58052/IEEXG02MT</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr"/>
@@ -22634,12 +22634,12 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02N7</t>
+          <t>wetland:10.58052/IEEXG02N7</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr"/>
@@ -22682,12 +22682,12 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NL</t>
+          <t>upland:10.58052/IEEXG02NL</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr"/>
@@ -22730,12 +22730,12 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NZ</t>
+          <t>transition:10.58052/IEEXG02NZ</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr"/>
@@ -22778,12 +22778,12 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OD</t>
+          <t>wetland:10.58052/IEEXG02OD</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr"/>
@@ -22826,12 +22826,12 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OR</t>
+          <t>upland:10.58052/IEEXG02OR</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr"/>
@@ -22874,12 +22874,12 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02P5</t>
+          <t>transition:10.58052/IEEXG02P5</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr"/>
@@ -22922,12 +22922,12 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PJ</t>
+          <t>wetland:10.58052/IEEXG02PJ</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr"/>
@@ -22970,12 +22970,12 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PX</t>
+          <t>upland:10.58052/IEEXG02PX</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr"/>
@@ -23018,12 +23018,12 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QB</t>
+          <t>transition:10.58052/IEEXG02QB</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr"/>
@@ -23066,12 +23066,12 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QP</t>
+          <t>wetland:10.58052/IEEXG02QP</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr"/>
@@ -23114,12 +23114,12 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02S9</t>
+          <t>upland:10.58052/IEEXG02S9</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr"/>
@@ -23162,12 +23162,12 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SN</t>
+          <t>transition:10.58052/IEEXG02SN</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr"/>
@@ -23210,12 +23210,12 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02T1</t>
+          <t>wetland:10.58052/IEEXG02T1</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr"/>
@@ -23258,12 +23258,12 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TF</t>
+          <t>upland:10.58052/IEEXG02TF</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr"/>
@@ -23306,12 +23306,12 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TT</t>
+          <t>transition:10.58052/IEEXG02TT</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr"/>
@@ -23354,12 +23354,12 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02U7</t>
+          <t>wetland:10.58052/IEEXG02U7</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr"/>
@@ -23402,12 +23402,12 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UL</t>
+          <t>upland:10.58052/IEEXG02UL</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr"/>
@@ -23450,12 +23450,12 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UZ</t>
+          <t>transition:10.58052/IEEXG02UZ</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr"/>
@@ -23498,12 +23498,12 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VD</t>
+          <t>wetland:10.58052/IEEXG02VD</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr"/>
@@ -23546,12 +23546,12 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VR</t>
+          <t>upland:10.58052/IEEXG02VR</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr"/>
@@ -23594,12 +23594,12 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02W5</t>
+          <t>transition:10.58052/IEEXG02W5</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr"/>
@@ -23642,12 +23642,12 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WJ</t>
+          <t>wetland:10.58052/IEEXG02WJ</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr"/>
@@ -23690,12 +23690,12 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WX</t>
+          <t>upland:10.58052/IEEXG02WX</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr"/>
@@ -23738,12 +23738,12 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02XB</t>
+          <t>transition:10.58052/IEEXG02XB</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr"/>
@@ -23786,12 +23786,12 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02XP</t>
+          <t>wetland:10.58052/IEEXG02XP</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr"/>
@@ -23834,12 +23834,12 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Y3</t>
+          <t>upland:10.58052/IEEXG02Y3</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr"/>
@@ -23882,12 +23882,12 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YH</t>
+          <t>transition:10.58052/IEEXG02YH</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr"/>
@@ -23930,12 +23930,12 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YV</t>
+          <t>wetland:10.58052/IEEXG02YV</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr"/>
@@ -23978,12 +23978,12 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Z9</t>
+          <t>upland:10.58052/IEEXG02Z9</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr"/>
@@ -24026,12 +24026,12 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZN</t>
+          <t>transition:10.58052/IEEXG02ZN</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr"/>
@@ -24074,12 +24074,12 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0301</t>
+          <t>wetland:10.58052/IEEXG0301</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr"/>
@@ -24122,12 +24122,12 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030F</t>
+          <t>upland:10.58052/IEEXG030F</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr"/>
@@ -24170,12 +24170,12 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030T</t>
+          <t>transition:10.58052/IEEXG030T</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr"/>
@@ -24218,12 +24218,12 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0317</t>
+          <t>wetland:10.58052/IEEXG0317</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr"/>
@@ -24266,12 +24266,12 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031L</t>
+          <t>upland:10.58052/IEEXG031L</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr"/>
@@ -24314,12 +24314,12 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031Z</t>
+          <t>transition:10.58052/IEEXG031Z</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr"/>
@@ -24362,12 +24362,12 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032D</t>
+          <t>wetland:10.58052/IEEXG032D</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr"/>
@@ -24410,12 +24410,12 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032R</t>
+          <t>upland:10.58052/IEEXG032R</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr"/>
@@ -24458,12 +24458,12 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0335</t>
+          <t>transition:10.58052/IEEXG0335</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr"/>
@@ -24506,12 +24506,12 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG033J</t>
+          <t>wetland:10.58052/IEEXG033J</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr"/>
@@ -24554,12 +24554,12 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0353</t>
+          <t>upland:10.58052/IEEXG0353</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr"/>
@@ -24602,12 +24602,12 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035H</t>
+          <t>transition:10.58052/IEEXG035H</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr"/>
@@ -24650,12 +24650,12 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035V</t>
+          <t>wetland:10.58052/IEEXG035V</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr"/>
@@ -24698,12 +24698,12 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020A</t>
+          <t>upland:10.58052/IEEXG020A</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr"/>
@@ -24746,12 +24746,12 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020O</t>
+          <t>transition:10.58052/IEEXG020O</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr"/>
@@ -24794,12 +24794,12 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0212</t>
+          <t>wetland:10.58052/IEEXG0212</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr"/>
@@ -24842,12 +24842,12 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021G</t>
+          <t>upland:10.58052/IEEXG021G</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr"/>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021U</t>
+          <t>transition:10.58052/IEEXG021U</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr"/>
@@ -24938,12 +24938,12 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0228</t>
+          <t>wetland:10.58052/IEEXG0228</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr"/>
@@ -24986,12 +24986,12 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022M</t>
+          <t>upland:10.58052/IEEXG022M</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr"/>
@@ -25034,12 +25034,12 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0230</t>
+          <t>transition:10.58052/IEEXG0230</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr"/>
@@ -25082,12 +25082,12 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023E</t>
+          <t>wetland:10.58052/IEEXG023E</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr"/>
@@ -25130,12 +25130,12 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023S</t>
+          <t>upland:10.58052/IEEXG023S</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr"/>
@@ -25178,12 +25178,12 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0246</t>
+          <t>transition:10.58052/IEEXG0246</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr"/>
@@ -25226,12 +25226,12 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024K</t>
+          <t>wetland:10.58052/IEEXG024K</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr"/>
@@ -25274,12 +25274,12 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024Y</t>
+          <t>upland:10.58052/IEEXG024Y</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr"/>
@@ -25322,12 +25322,12 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025C</t>
+          <t>transition:10.58052/IEEXG025C</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr"/>
@@ -25370,12 +25370,12 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025Q</t>
+          <t>wetland:10.58052/IEEXG025Q</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr"/>
@@ -25418,12 +25418,12 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0264</t>
+          <t>upland:10.58052/IEEXG0264</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr"/>
@@ -25466,12 +25466,12 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026I</t>
+          <t>transition:10.58052/IEEXG026I</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr"/>
@@ -25514,12 +25514,12 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026W</t>
+          <t>wetland:10.58052/IEEXG026W</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr"/>
@@ -25562,12 +25562,12 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027A</t>
+          <t>upland:10.58052/IEEXG027A</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr"/>
@@ -25610,12 +25610,12 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027O</t>
+          <t>transition:10.58052/IEEXG027O</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr"/>
@@ -25658,12 +25658,12 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0282</t>
+          <t>wetland:10.58052/IEEXG0282</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr"/>
@@ -25706,12 +25706,12 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028G</t>
+          <t>upland:10.58052/IEEXG028G</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr"/>
@@ -25754,12 +25754,12 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028U</t>
+          <t>transition:10.58052/IEEXG028U</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr"/>
@@ -25802,12 +25802,12 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0298</t>
+          <t>wetland:10.58052/IEEXG0298</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr"/>
@@ -25850,12 +25850,12 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG029M</t>
+          <t>upland:10.58052/IEEXG029M</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr"/>
@@ -25898,12 +25898,12 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02A0</t>
+          <t>transition:10.58052/IEEXG02A0</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr"/>
@@ -25946,12 +25946,12 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AE</t>
+          <t>wetland:10.58052/IEEXG02AE</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr"/>
@@ -25994,12 +25994,12 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AS</t>
+          <t>upland:10.58052/IEEXG02AS</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr"/>
@@ -26042,12 +26042,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02B6</t>
+          <t>transition:10.58052/IEEXG02B6</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr"/>
@@ -26090,12 +26090,12 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BK</t>
+          <t>wetland:10.58052/IEEXG02BK</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr"/>
@@ -26138,12 +26138,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BY</t>
+          <t>upland:10.58052/IEEXG02BY</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr"/>
@@ -26186,12 +26186,12 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CC</t>
+          <t>transition:10.58052/IEEXG02CC</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr"/>
@@ -26234,12 +26234,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CQ</t>
+          <t>wetland:10.58052/IEEXG02CQ</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr"/>
@@ -26282,12 +26282,12 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02D4</t>
+          <t>upland:10.58052/IEEXG02D4</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr"/>
@@ -26330,12 +26330,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DI</t>
+          <t>transition:10.58052/IEEXG02DI</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr"/>
@@ -26378,12 +26378,12 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DW</t>
+          <t>wetland:10.58052/IEEXG02DW</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr"/>
@@ -26426,12 +26426,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EA</t>
+          <t>upland:10.58052/IEEXG02EA</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr"/>
@@ -26474,12 +26474,12 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EO</t>
+          <t>transition:10.58052/IEEXG02EO</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr"/>
@@ -26522,12 +26522,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02F2</t>
+          <t>wetland:10.58052/IEEXG02F2</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr"/>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FG</t>
+          <t>upland:10.58052/IEEXG02FG</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr"/>
@@ -26618,12 +26618,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FU</t>
+          <t>transition:10.58052/IEEXG02FU</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr"/>
@@ -26666,12 +26666,12 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02G8</t>
+          <t>wetland:10.58052/IEEXG02G8</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr"/>
@@ -26714,12 +26714,12 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GM</t>
+          <t>upland:10.58052/IEEXG02GM</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr"/>
@@ -26762,12 +26762,12 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02H0</t>
+          <t>transition:10.58052/IEEXG02H0</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr"/>
@@ -26810,12 +26810,12 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HE</t>
+          <t>wetland:10.58052/IEEXG02HE</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr"/>
@@ -26858,12 +26858,12 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HS</t>
+          <t>upland:10.58052/IEEXG02HS</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr"/>
@@ -26906,12 +26906,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02I6</t>
+          <t>transition:10.58052/IEEXG02I6</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr"/>
@@ -26954,12 +26954,12 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IK</t>
+          <t>wetland:10.58052/IEEXG02IK</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr"/>
@@ -27002,12 +27002,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IY</t>
+          <t>upland:10.58052/IEEXG02IY</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr"/>
@@ -27050,12 +27050,12 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JC</t>
+          <t>transition:10.58052/IEEXG02JC</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr"/>
@@ -27098,12 +27098,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JQ</t>
+          <t>wetland:10.58052/IEEXG02JQ</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr"/>
@@ -27146,12 +27146,12 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02K4</t>
+          <t>upland:10.58052/IEEXG02K4</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr"/>
@@ -27194,12 +27194,12 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KI</t>
+          <t>transition:10.58052/IEEXG02KI</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr"/>
@@ -27242,12 +27242,12 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KW</t>
+          <t>wetland:10.58052/IEEXG02KW</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr"/>
@@ -27290,12 +27290,12 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LA</t>
+          <t>upland:10.58052/IEEXG02LA</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr"/>
@@ -27338,12 +27338,12 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LO</t>
+          <t>transition:10.58052/IEEXG02LO</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr"/>
@@ -27386,12 +27386,12 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02M2</t>
+          <t>wetland:10.58052/IEEXG02M2</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr"/>
@@ -27434,12 +27434,12 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MG</t>
+          <t>upland:10.58052/IEEXG02MG</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr"/>
@@ -27482,12 +27482,12 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MU</t>
+          <t>transition:10.58052/IEEXG02MU</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr"/>
@@ -27530,12 +27530,12 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02N8</t>
+          <t>wetland:10.58052/IEEXG02N8</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr"/>
@@ -27578,12 +27578,12 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NM</t>
+          <t>upland:10.58052/IEEXG02NM</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr"/>
@@ -27626,12 +27626,12 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02O0</t>
+          <t>transition:10.58052/IEEXG02O0</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr"/>
@@ -27674,12 +27674,12 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OE</t>
+          <t>wetland:10.58052/IEEXG02OE</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr"/>
@@ -27722,12 +27722,12 @@
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OS</t>
+          <t>upland:10.58052/IEEXG02OS</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr"/>
@@ -27770,12 +27770,12 @@
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02P6</t>
+          <t>transition:10.58052/IEEXG02P6</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr"/>
@@ -27818,12 +27818,12 @@
       </c>
       <c r="C543" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PK</t>
+          <t>wetland:10.58052/IEEXG02PK</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr"/>
@@ -27866,12 +27866,12 @@
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PY</t>
+          <t>upland:10.58052/IEEXG02PY</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr"/>
@@ -27914,12 +27914,12 @@
       </c>
       <c r="C545" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QC</t>
+          <t>transition:10.58052/IEEXG02QC</t>
         </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E545" s="2" t="inlineStr"/>
@@ -27962,12 +27962,12 @@
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QQ</t>
+          <t>wetland:10.58052/IEEXG02QQ</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr"/>
@@ -28010,12 +28010,12 @@
       </c>
       <c r="C547" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SA</t>
+          <t>upland:10.58052/IEEXG02SA</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E547" s="2" t="inlineStr"/>
@@ -28058,12 +28058,12 @@
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SO</t>
+          <t>transition:10.58052/IEEXG02SO</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr"/>
@@ -28106,12 +28106,12 @@
       </c>
       <c r="C549" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02T2</t>
+          <t>wetland:10.58052/IEEXG02T2</t>
         </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E549" s="2" t="inlineStr"/>
@@ -28154,12 +28154,12 @@
       </c>
       <c r="C550" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TG</t>
+          <t>upland:10.58052/IEEXG02TG</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E550" s="2" t="inlineStr"/>
@@ -28202,12 +28202,12 @@
       </c>
       <c r="C551" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TU</t>
+          <t>transition:10.58052/IEEXG02TU</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E551" s="2" t="inlineStr"/>
@@ -28250,12 +28250,12 @@
       </c>
       <c r="C552" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02U8</t>
+          <t>wetland:10.58052/IEEXG02U8</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E552" s="2" t="inlineStr"/>
@@ -28298,12 +28298,12 @@
       </c>
       <c r="C553" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UM</t>
+          <t>upland:10.58052/IEEXG02UM</t>
         </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E553" s="2" t="inlineStr"/>
@@ -28346,12 +28346,12 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02V0</t>
+          <t>transition:10.58052/IEEXG02V0</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr"/>
@@ -28394,12 +28394,12 @@
       </c>
       <c r="C555" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VE</t>
+          <t>wetland:10.58052/IEEXG02VE</t>
         </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E555" s="2" t="inlineStr"/>
@@ -28442,12 +28442,12 @@
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VS</t>
+          <t>upland:10.58052/IEEXG02VS</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr"/>
@@ -28490,12 +28490,12 @@
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02W6</t>
+          <t>transition:10.58052/IEEXG02W6</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E557" s="2" t="inlineStr"/>
@@ -28538,12 +28538,12 @@
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WK</t>
+          <t>wetland:10.58052/IEEXG02WK</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr"/>
@@ -28586,12 +28586,12 @@
       </c>
       <c r="C559" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Y4</t>
+          <t>upland:10.58052/IEEXG02Y4</t>
         </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E559" s="2" t="inlineStr"/>
@@ -28634,12 +28634,12 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YI</t>
+          <t>transition:10.58052/IEEXG02YI</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr"/>
@@ -28682,12 +28682,12 @@
       </c>
       <c r="C561" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YW</t>
+          <t>wetland:10.58052/IEEXG02YW</t>
         </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E561" s="2" t="inlineStr"/>
@@ -28730,12 +28730,12 @@
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZA</t>
+          <t>upland:10.58052/IEEXG02ZA</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E562" s="2" t="inlineStr"/>
@@ -28778,12 +28778,12 @@
       </c>
       <c r="C563" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZO</t>
+          <t>transition:10.58052/IEEXG02ZO</t>
         </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E563" s="2" t="inlineStr"/>
@@ -28826,12 +28826,12 @@
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0302</t>
+          <t>wetland:10.58052/IEEXG0302</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr"/>
@@ -28874,12 +28874,12 @@
       </c>
       <c r="C565" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030G</t>
+          <t>upland:10.58052/IEEXG030G</t>
         </is>
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E565" s="2" t="inlineStr"/>
@@ -28922,12 +28922,12 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030U</t>
+          <t>transition:10.58052/IEEXG030U</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr"/>
@@ -28970,12 +28970,12 @@
       </c>
       <c r="C567" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0318</t>
+          <t>wetland:10.58052/IEEXG0318</t>
         </is>
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E567" s="2" t="inlineStr"/>
@@ -29018,12 +29018,12 @@
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031M</t>
+          <t>upland:10.58052/IEEXG031M</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E568" s="2" t="inlineStr"/>
@@ -29066,12 +29066,12 @@
       </c>
       <c r="C569" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0320</t>
+          <t>transition:10.58052/IEEXG0320</t>
         </is>
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E569" s="2" t="inlineStr"/>
@@ -29114,12 +29114,12 @@
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032E</t>
+          <t>wetland:10.58052/IEEXG032E</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr"/>
@@ -29162,12 +29162,12 @@
       </c>
       <c r="C571" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032S</t>
+          <t>upland:10.58052/IEEXG032S</t>
         </is>
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E571" s="2" t="inlineStr"/>
@@ -29210,12 +29210,12 @@
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0336</t>
+          <t>transition:10.58052/IEEXG0336</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr"/>
@@ -29258,12 +29258,12 @@
       </c>
       <c r="C573" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG033K</t>
+          <t>wetland:10.58052/IEEXG033K</t>
         </is>
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E573" s="2" t="inlineStr"/>
@@ -29306,12 +29306,12 @@
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0354</t>
+          <t>upland:10.58052/IEEXG0354</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr"/>
@@ -29354,12 +29354,12 @@
       </c>
       <c r="C575" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035I</t>
+          <t>transition:10.58052/IEEXG035I</t>
         </is>
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E575" s="2" t="inlineStr"/>
@@ -29402,12 +29402,12 @@
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035W</t>
+          <t>wetland:10.58052/IEEXG035W</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr"/>
